--- a/results/results_baseline.xlsx
+++ b/results/results_baseline.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15540"/>
+    <workbookView windowWidth="22992" windowHeight="9240"/>
   </bookViews>
   <sheets>
-    <sheet name="test_domain" sheetId="4" r:id="rId1"/>
-    <sheet name="origin_domain_num" sheetId="5" r:id="rId2"/>
+    <sheet name="conv2d_O" sheetId="4" r:id="rId1"/>
+    <sheet name="conv2d_T" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
     <t>HyperParameters</t>
   </si>
   <si>
-    <t>test_domain</t>
+    <t>Origin_domain_nums</t>
   </si>
   <si>
     <t>VAL_ACC</t>
@@ -57,6 +57,15 @@
     <t>kernel_size</t>
   </si>
   <si>
+    <t>out_channels</t>
+  </si>
+  <si>
+    <t>stride</t>
+  </si>
+  <si>
+    <t>test_domain</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
@@ -71,15 +80,6 @@
   <si>
     <t>331</t>
   </si>
-  <si>
-    <t>out_channels</t>
-  </si>
-  <si>
-    <t>stride</t>
-  </si>
-  <si>
-    <t>Origin_domain_nums</t>
-  </si>
 </sst>
 </file>
 
@@ -91,7 +91,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,12 +101,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -257,18 +251,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -620,52 +608,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
@@ -680,85 +671,80 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1105,6 +1091,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>99.9502658843994</v>
+      </c>
+      <c r="D2">
+        <v>99.9029278755188</v>
+      </c>
+      <c r="E2">
+        <v>95.589</v>
+      </c>
+      <c r="F2">
+        <v>95.679</v>
+      </c>
+      <c r="G2">
+        <v>95.589</v>
+      </c>
+      <c r="H2">
+        <v>95.868</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>99.9536544084549</v>
+      </c>
+      <c r="D3">
+        <v>99.904465675354</v>
+      </c>
+      <c r="E3">
+        <v>96.885</v>
+      </c>
+      <c r="F3">
+        <v>96.949</v>
+      </c>
+      <c r="G3">
+        <v>96.885</v>
+      </c>
+      <c r="H3">
+        <v>97.114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>99.9706149101257</v>
+      </c>
+      <c r="D4">
+        <v>99.9578475952148</v>
+      </c>
+      <c r="E4">
+        <v>96.953</v>
+      </c>
+      <c r="F4">
+        <v>96.944</v>
+      </c>
+      <c r="G4">
+        <v>96.953</v>
+      </c>
+      <c r="H4">
+        <v>96.959</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>99.9310523271561</v>
+      </c>
+      <c r="D5">
+        <v>99.9264895915985</v>
+      </c>
+      <c r="E5">
+        <v>98.768</v>
+      </c>
+      <c r="F5">
+        <v>98.793</v>
+      </c>
+      <c r="G5">
+        <v>98.768</v>
+      </c>
+      <c r="H5">
+        <v>98.859</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>99.6541142463684</v>
+      </c>
+      <c r="D6">
+        <v>99.4312644004822</v>
+      </c>
+      <c r="E6">
+        <v>58.65</v>
+      </c>
+      <c r="F6">
+        <v>58.067</v>
+      </c>
+      <c r="G6">
+        <v>58.65</v>
+      </c>
+      <c r="H6">
+        <v>63.79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>99.4416028261185</v>
+      </c>
+      <c r="D7">
+        <v>98.7696290016174</v>
+      </c>
+      <c r="E7">
+        <v>66.892</v>
+      </c>
+      <c r="F7">
+        <v>64.952</v>
+      </c>
+      <c r="G7">
+        <v>66.892</v>
+      </c>
+      <c r="H7">
+        <v>66.101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>99.5056629180908</v>
+      </c>
+      <c r="D8">
+        <v>98.8088846206665</v>
+      </c>
+      <c r="E8">
+        <v>75.784</v>
+      </c>
+      <c r="F8">
+        <v>76.048</v>
+      </c>
+      <c r="G8">
+        <v>75.784</v>
+      </c>
+      <c r="H8">
+        <v>77.435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1">
+        <v>4</v>
+      </c>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9">
+        <v>87.756</v>
+      </c>
+      <c r="F9">
+        <v>90.076</v>
+      </c>
+      <c r="G9">
+        <v>87.756</v>
+      </c>
+      <c r="H9">
+        <v>87.555</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>99.762624502182</v>
+      </c>
+      <c r="D10">
+        <v>99.39204454422</v>
+      </c>
+      <c r="E10">
+        <v>92.176</v>
+      </c>
+      <c r="F10">
+        <v>92.451</v>
+      </c>
+      <c r="G10">
+        <v>92.176</v>
+      </c>
+      <c r="H10">
+        <v>92.846</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>99.8507916927338</v>
+      </c>
+      <c r="D11">
+        <v>99.6149659156799</v>
+      </c>
+      <c r="E11">
+        <v>95.824</v>
+      </c>
+      <c r="F11">
+        <v>95.792</v>
+      </c>
+      <c r="G11">
+        <v>95.824</v>
+      </c>
+      <c r="H11">
+        <v>95.766</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>99.8688817024231</v>
+      </c>
+      <c r="D12">
+        <v>99.6618032455444</v>
+      </c>
+      <c r="E12">
+        <v>96.33</v>
+      </c>
+      <c r="F12">
+        <v>96.28</v>
+      </c>
+      <c r="G12">
+        <v>96.33</v>
+      </c>
+      <c r="H12">
+        <v>96.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="3"/>
+      <c r="B13" s="1">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>99.6823728084564</v>
+      </c>
+      <c r="D13">
+        <v>99.176812171936</v>
+      </c>
+      <c r="E13">
+        <v>97.825</v>
+      </c>
+      <c r="F13">
+        <v>97.771</v>
+      </c>
+      <c r="G13">
+        <v>97.825</v>
+      </c>
+      <c r="H13">
+        <v>97.787</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
@@ -1113,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1139,7 +1458,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>99.9107033014297</v>
@@ -1148,22 +1467,22 @@
         <v>99.9189853668213</v>
       </c>
       <c r="E2">
-        <v>99.689</v>
+        <v>99.471</v>
       </c>
       <c r="F2">
-        <v>89.608</v>
+        <v>99.471</v>
       </c>
       <c r="G2">
-        <v>90.246</v>
+        <v>99.471</v>
       </c>
       <c r="H2">
-        <v>89.108</v>
+        <v>99.472</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>99.8767912387848</v>
@@ -1172,22 +1491,22 @@
         <v>99.8790264129639</v>
       </c>
       <c r="E3">
-        <v>99.897</v>
+        <v>99.851</v>
       </c>
       <c r="F3">
-        <v>90.244</v>
+        <v>99.851</v>
       </c>
       <c r="G3">
-        <v>90.475</v>
+        <v>99.851</v>
       </c>
       <c r="H3">
-        <v>90.021</v>
+        <v>99.851</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>99.7208029031754</v>
@@ -1196,46 +1515,46 @@
         <v>99.786901473999</v>
       </c>
       <c r="E4">
-        <v>99.7</v>
+        <v>99.399</v>
       </c>
       <c r="F4">
-        <v>89.898</v>
+        <v>99.399</v>
       </c>
       <c r="G4">
-        <v>90.256</v>
+        <v>99.399</v>
       </c>
       <c r="H4">
-        <v>89.568</v>
+        <v>99.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>99.9429166316986</v>
+        <v>99.8654901981354</v>
       </c>
       <c r="D5">
-        <v>99.9349296092987</v>
+        <v>99.8395085334778</v>
       </c>
       <c r="E5">
-        <v>98.418</v>
+        <v>99.916</v>
       </c>
       <c r="F5">
-        <v>87.123</v>
+        <v>99.916</v>
       </c>
       <c r="G5">
-        <v>88.839</v>
+        <v>99.916</v>
       </c>
       <c r="H5">
-        <v>85.83</v>
+        <v>99.917</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>99.9310523271561</v>
@@ -1244,24 +1563,24 @@
         <v>99.9264895915985</v>
       </c>
       <c r="E6">
-        <v>98.978</v>
+        <v>98.768</v>
       </c>
       <c r="F6">
-        <v>86.333</v>
+        <v>98.793</v>
       </c>
       <c r="G6">
-        <v>89.989</v>
+        <v>98.768</v>
       </c>
       <c r="H6">
-        <v>83.608</v>
+        <v>98.859</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>98.1462210416794</v>
@@ -1269,23 +1588,23 @@
       <c r="D7">
         <v>97.713303565979</v>
       </c>
-      <c r="E7" s="5">
-        <v>95.41</v>
+      <c r="E7">
+        <v>94.781</v>
       </c>
       <c r="F7">
-        <v>78.143</v>
+        <v>94.69</v>
       </c>
       <c r="G7">
-        <v>76.589</v>
+        <v>94.781</v>
       </c>
       <c r="H7">
-        <v>80.254</v>
+        <v>94.811</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>98.9267349243164</v>
@@ -1294,22 +1613,22 @@
         <v>98.3689963817596</v>
       </c>
       <c r="E8">
-        <v>95.654</v>
+        <v>94.25</v>
       </c>
       <c r="F8">
-        <v>78.518</v>
+        <v>94.009</v>
       </c>
       <c r="G8">
-        <v>77.344</v>
+        <v>94.25</v>
       </c>
       <c r="H8">
-        <v>80.55</v>
+        <v>94.412</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <v>99.3822634220123</v>
@@ -1317,73 +1636,69 @@
       <c r="D9">
         <v>98.8369405269623</v>
       </c>
-      <c r="E9" s="5">
-        <v>96.162</v>
+      <c r="E9">
+        <v>95.282</v>
       </c>
       <c r="F9">
-        <v>78.522</v>
+        <v>95.131</v>
       </c>
       <c r="G9">
-        <v>77.049</v>
+        <v>95.282</v>
       </c>
       <c r="H9">
-        <v>81.056</v>
+        <v>95.415</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>99.5495527982712</v>
+        <v>98.7204372882843</v>
       </c>
       <c r="D10">
-        <v>99.246883392334</v>
+        <v>98.056972026825</v>
       </c>
       <c r="E10">
-        <v>72.826</v>
+        <v>98.859</v>
       </c>
       <c r="F10">
-        <v>54.573</v>
+        <v>98.856</v>
       </c>
       <c r="G10">
-        <v>60.032</v>
+        <v>98.859</v>
       </c>
       <c r="H10">
-        <v>53.368</v>
+        <v>98.871</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>99.2986142635345</v>
-      </c>
-      <c r="D11">
-        <v>98.9125370979309</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11"/>
       <c r="E11">
-        <v>87.517</v>
+        <v>87.756</v>
       </c>
       <c r="F11">
-        <v>68.634</v>
+        <v>90.076</v>
       </c>
       <c r="G11">
-        <v>68.207</v>
+        <v>87.756</v>
       </c>
       <c r="H11">
-        <v>73.359</v>
+        <v>87.555</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>99.6439397335052</v>
@@ -1392,22 +1707,22 @@
         <v>99.0898489952087</v>
       </c>
       <c r="E12">
-        <v>94.465</v>
+        <v>95.362</v>
       </c>
       <c r="F12">
-        <v>89.409</v>
+        <v>95.506</v>
       </c>
       <c r="G12">
-        <v>93.271</v>
+        <v>95.362</v>
       </c>
       <c r="H12">
-        <v>86.587</v>
+        <v>95.758</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <v>99.1720199584961</v>
@@ -1416,22 +1731,22 @@
         <v>97.8589236736298</v>
       </c>
       <c r="E13">
-        <v>98.756</v>
+        <v>97.951</v>
       </c>
       <c r="F13">
-        <v>96.699</v>
+        <v>97.899</v>
       </c>
       <c r="G13">
-        <v>95.389</v>
+        <v>97.951</v>
       </c>
       <c r="H13">
-        <v>98.141</v>
+        <v>97.922</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <v>99.625289440155</v>
@@ -1440,46 +1755,46 @@
         <v>99.0249037742615</v>
       </c>
       <c r="E14">
-        <v>98.79</v>
+        <v>97.464</v>
       </c>
       <c r="F14">
-        <v>96.529</v>
+        <v>97.336</v>
       </c>
       <c r="G14">
-        <v>94.895</v>
+        <v>97.464</v>
       </c>
       <c r="H14">
-        <v>98.481</v>
+        <v>97.49</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15">
-        <v>99.7417151927948</v>
+        <v>99.597030878067</v>
       </c>
       <c r="D15">
-        <v>99.3302583694458</v>
+        <v>98.9554226398468</v>
       </c>
       <c r="E15">
-        <v>72.556</v>
+        <v>99.185</v>
       </c>
       <c r="F15">
-        <v>63.673</v>
+        <v>99.178</v>
       </c>
       <c r="G15">
-        <v>74.322</v>
+        <v>99.185</v>
       </c>
       <c r="H15">
-        <v>64.538</v>
+        <v>99.181</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <v>99.6823728084564</v>
@@ -1488,16 +1803,16 @@
         <v>99.176812171936</v>
       </c>
       <c r="E16">
-        <v>98.445</v>
+        <v>97.825</v>
       </c>
       <c r="F16">
-        <v>95.932</v>
+        <v>97.771</v>
       </c>
       <c r="G16">
-        <v>94.407</v>
+        <v>97.825</v>
       </c>
       <c r="H16">
-        <v>97.647</v>
+        <v>97.787</v>
       </c>
     </row>
   </sheetData>
@@ -1509,341 +1824,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>99.9502658843994</v>
-      </c>
-      <c r="D2">
-        <v>99.9029278755188</v>
-      </c>
-      <c r="E2" s="4">
-        <v>97.366</v>
-      </c>
-      <c r="F2">
-        <v>80.871</v>
-      </c>
-      <c r="G2">
-        <v>86.232</v>
-      </c>
-      <c r="H2">
-        <v>77.711</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>99.9536544084549</v>
-      </c>
-      <c r="D3">
-        <v>99.904465675354</v>
-      </c>
-      <c r="E3">
-        <v>98.236</v>
-      </c>
-      <c r="F3">
-        <v>84.414</v>
-      </c>
-      <c r="G3">
-        <v>89.329</v>
-      </c>
-      <c r="H3">
-        <v>81.008</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>99.9706149101257</v>
-      </c>
-      <c r="D4">
-        <v>99.9578475952148</v>
-      </c>
-      <c r="E4">
-        <v>98.351</v>
-      </c>
-      <c r="F4">
-        <v>86.715</v>
-      </c>
-      <c r="G4">
-        <v>88.956</v>
-      </c>
-      <c r="H4">
-        <v>85.002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>99.9310523271561</v>
-      </c>
-      <c r="D5">
-        <v>99.9264895915985</v>
-      </c>
-      <c r="E5">
-        <v>98.978</v>
-      </c>
-      <c r="F5">
-        <v>86.333</v>
-      </c>
-      <c r="G5">
-        <v>89.989</v>
-      </c>
-      <c r="H5">
-        <v>83.608</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>99.6541142463684</v>
-      </c>
-      <c r="D6">
-        <v>99.4312644004822</v>
-      </c>
-      <c r="E6">
-        <v>59.333</v>
-      </c>
-      <c r="F6">
-        <v>39.672</v>
-      </c>
-      <c r="G6">
-        <v>40.956</v>
-      </c>
-      <c r="H6">
-        <v>43.888</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>99.4416028261185</v>
-      </c>
-      <c r="D7">
-        <v>98.7696290016174</v>
-      </c>
-      <c r="E7">
-        <v>67.16</v>
-      </c>
-      <c r="F7">
-        <v>45.959</v>
-      </c>
-      <c r="G7">
-        <v>46.026</v>
-      </c>
-      <c r="H7">
-        <v>48.861</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>99.5056629180908</v>
-      </c>
-      <c r="D8">
-        <v>98.8088846206665</v>
-      </c>
-      <c r="E8">
-        <v>73.813</v>
-      </c>
-      <c r="F8">
-        <v>55.127</v>
-      </c>
-      <c r="G8">
-        <v>56.906</v>
-      </c>
-      <c r="H8">
-        <v>55.444</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="1">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>99.2986142635345</v>
-      </c>
-      <c r="D9">
-        <v>98.9125370979309</v>
-      </c>
-      <c r="E9">
-        <v>87.517</v>
-      </c>
-      <c r="F9">
-        <v>68.634</v>
-      </c>
-      <c r="G9">
-        <v>68.207</v>
-      </c>
-      <c r="H9">
-        <v>73.359</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>99.762624502182</v>
-      </c>
-      <c r="D10">
-        <v>99.39204454422</v>
-      </c>
-      <c r="E10">
-        <v>94.565</v>
-      </c>
-      <c r="F10">
-        <v>88.054</v>
-      </c>
-      <c r="G10">
-        <v>89.194</v>
-      </c>
-      <c r="H10">
-        <v>87.094</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>99.8507916927338</v>
-      </c>
-      <c r="D11">
-        <v>99.6149659156799</v>
-      </c>
-      <c r="E11">
-        <v>97.158</v>
-      </c>
-      <c r="F11">
-        <v>93.159</v>
-      </c>
-      <c r="G11">
-        <v>92.768</v>
-      </c>
-      <c r="H11">
-        <v>93.576</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>99.8688817024231</v>
-      </c>
-      <c r="D12">
-        <v>99.6618032455444</v>
-      </c>
-      <c r="E12">
-        <v>97.6</v>
-      </c>
-      <c r="F12">
-        <v>93.941</v>
-      </c>
-      <c r="G12">
-        <v>92.737</v>
-      </c>
-      <c r="H12">
-        <v>95.281</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
-      <c r="B13" s="1">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>99.6823728084564</v>
-      </c>
-      <c r="D13">
-        <v>99.176812171936</v>
-      </c>
-      <c r="E13">
-        <v>98.445</v>
-      </c>
-      <c r="F13">
-        <v>95.932</v>
-      </c>
-      <c r="G13">
-        <v>94.407</v>
-      </c>
-      <c r="H13">
-        <v>97.647</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/results/results_baseline.xlsx
+++ b/results/results_baseline.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22992" windowHeight="9240"/>
+    <workbookView windowWidth="30720" windowHeight="15540" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="conv2d_O" sheetId="4" r:id="rId1"/>
@@ -91,7 +91,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -608,143 +615,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1095,36 +1108,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
       <c r="C2">
@@ -1147,8 +1160,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1">
+      <c r="A3" s="4"/>
+      <c r="B3" s="2">
         <v>2</v>
       </c>
       <c r="C3">
@@ -1171,8 +1184,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1">
+      <c r="A4" s="4"/>
+      <c r="B4" s="2">
         <v>3</v>
       </c>
       <c r="C4">
@@ -1195,8 +1208,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1">
+      <c r="A5" s="5"/>
+      <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5">
@@ -1218,105 +1231,109 @@
         <v>98.859</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:8">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="3">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>99.6541142463684</v>
-      </c>
-      <c r="D6">
-        <v>99.4312644004822</v>
-      </c>
-      <c r="E6">
-        <v>58.65</v>
-      </c>
-      <c r="F6">
-        <v>58.067</v>
-      </c>
-      <c r="G6">
-        <v>58.65</v>
-      </c>
-      <c r="H6">
-        <v>63.79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1">
+      <c r="C6" s="1">
+        <v>97.7147656198201</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>62.172</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
+      <c r="A7" s="6"/>
+      <c r="B7" s="3">
         <v>2</v>
       </c>
-      <c r="C7">
-        <v>99.4416028261185</v>
-      </c>
-      <c r="D7">
-        <v>98.7696290016174</v>
-      </c>
-      <c r="E7">
-        <v>66.892</v>
-      </c>
-      <c r="F7">
-        <v>64.952</v>
-      </c>
-      <c r="G7">
-        <v>66.892</v>
-      </c>
-      <c r="H7">
-        <v>66.101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1">
+      <c r="C7" s="1">
+        <v>97.8451610051495</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>71.545</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:8">
+      <c r="A8" s="6"/>
+      <c r="B8" s="3">
         <v>3</v>
       </c>
-      <c r="C8">
-        <v>99.5056629180908</v>
-      </c>
-      <c r="D8">
-        <v>98.8088846206665</v>
-      </c>
-      <c r="E8">
-        <v>75.784</v>
-      </c>
-      <c r="F8">
-        <v>76.048</v>
-      </c>
-      <c r="G8">
-        <v>75.784</v>
-      </c>
-      <c r="H8">
-        <v>77.435</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="1">
+      <c r="C8" s="1">
+        <v>97.8856793452236</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>81.32</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:8">
+      <c r="A9" s="7"/>
+      <c r="B9" s="3">
         <v>4</v>
       </c>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9">
-        <v>87.756</v>
-      </c>
-      <c r="F9">
-        <v>90.076</v>
-      </c>
-      <c r="G9">
-        <v>87.756</v>
-      </c>
-      <c r="H9">
-        <v>87.555</v>
+      <c r="C9" s="1">
+        <v>97.257829248348</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>87.731</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2">
         <v>1</v>
       </c>
       <c r="C10">
@@ -1339,8 +1356,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1">
+      <c r="A11" s="4"/>
+      <c r="B11" s="2">
         <v>2</v>
       </c>
       <c r="C11">
@@ -1363,8 +1380,8 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1">
+      <c r="A12" s="4"/>
+      <c r="B12" s="2">
         <v>3</v>
       </c>
       <c r="C12">
@@ -1387,8 +1404,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
-      <c r="B13" s="1">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2">
         <v>4</v>
       </c>
       <c r="C13">
@@ -1428,36 +1445,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2">
@@ -1480,8 +1497,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C3">
@@ -1504,8 +1521,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C4">
@@ -1528,8 +1545,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C5">
@@ -1552,8 +1569,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6">
@@ -1575,129 +1592,133 @@
         <v>98.859</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
+    <row r="7" s="1" customFormat="1" spans="1:8">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7">
-        <v>98.1462210416794</v>
-      </c>
-      <c r="D7">
-        <v>97.713303565979</v>
-      </c>
-      <c r="E7">
-        <v>94.781</v>
-      </c>
-      <c r="F7">
-        <v>94.69</v>
-      </c>
-      <c r="G7">
-        <v>94.781</v>
-      </c>
-      <c r="H7">
-        <v>94.811</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
+      <c r="C7" s="1">
+        <v>97.2202576966429</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>90.808</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:8">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C8">
-        <v>98.9267349243164</v>
-      </c>
-      <c r="D8">
-        <v>98.3689963817596</v>
-      </c>
-      <c r="E8">
-        <v>94.25</v>
-      </c>
-      <c r="F8">
-        <v>94.009</v>
-      </c>
-      <c r="G8">
-        <v>94.25</v>
-      </c>
-      <c r="H8">
-        <v>94.412</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
+      <c r="C8" s="1">
+        <v>97.2230203107388</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>91.56</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:8">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C9">
-        <v>99.3822634220123</v>
-      </c>
-      <c r="D9">
-        <v>98.8369405269623</v>
-      </c>
-      <c r="E9">
-        <v>95.282</v>
-      </c>
-      <c r="F9">
-        <v>95.131</v>
-      </c>
-      <c r="G9">
-        <v>95.282</v>
-      </c>
-      <c r="H9">
-        <v>95.415</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
+      <c r="C9" s="1">
+        <v>97.3489955135147</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>91.857</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:8">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C10">
-        <v>98.7204372882843</v>
-      </c>
-      <c r="D10">
-        <v>98.056972026825</v>
-      </c>
-      <c r="E10">
-        <v>98.859</v>
-      </c>
-      <c r="F10">
-        <v>98.856</v>
-      </c>
-      <c r="G10">
-        <v>98.859</v>
-      </c>
-      <c r="H10">
-        <v>98.871</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
+      <c r="C10" s="1">
+        <v>97.4611576458108</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>54.616</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:8">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11">
-        <v>87.756</v>
-      </c>
-      <c r="F11">
-        <v>90.076</v>
-      </c>
-      <c r="G11">
-        <v>87.756</v>
-      </c>
-      <c r="H11">
-        <v>87.555</v>
+      <c r="C11" s="1">
+        <v>97.257829248348</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>87.731</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12">
@@ -1720,8 +1741,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C13">
@@ -1744,8 +1765,8 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C14">
@@ -1768,8 +1789,8 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C15">
@@ -1792,8 +1813,8 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16">

--- a/results/results_baseline.xlsx
+++ b/results/results_baseline.xlsx
@@ -4,11 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15540" activeTab="1"/>
+    <workbookView windowWidth="30720" windowHeight="15540" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="conv2d_O" sheetId="4" r:id="rId1"/>
     <sheet name="conv2d_T" sheetId="5" r:id="rId2"/>
+    <sheet name="conv2d_T_half" sheetId="6" r:id="rId3"/>
+    <sheet name="conv2d_T_quarter" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="17">
   <si>
     <t>HyperParameters</t>
   </si>
@@ -100,15 +102,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -745,19 +747,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1108,36 +1118,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
       <c r="C2">
@@ -1160,8 +1170,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="4"/>
-      <c r="B3" s="2">
+      <c r="A3" s="8"/>
+      <c r="B3" s="6">
         <v>2</v>
       </c>
       <c r="C3">
@@ -1184,8 +1194,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="4"/>
-      <c r="B4" s="2">
+      <c r="A4" s="8"/>
+      <c r="B4" s="6">
         <v>3</v>
       </c>
       <c r="C4">
@@ -1208,8 +1218,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="5"/>
-      <c r="B5" s="2">
+      <c r="A5" s="9"/>
+      <c r="B5" s="6">
         <v>4</v>
       </c>
       <c r="C5">
@@ -1231,109 +1241,109 @@
         <v>98.859</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="A6" s="3" t="s">
+    <row r="6" s="5" customFormat="1" spans="1:8">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="7">
         <v>1</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="5">
         <v>97.7147656198201</v>
       </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
         <v>62.172</v>
       </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="A7" s="6"/>
-      <c r="B7" s="3">
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="5" customFormat="1" spans="1:8">
+      <c r="A7" s="10"/>
+      <c r="B7" s="7">
         <v>2</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="5">
         <v>97.8451610051495</v>
       </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
         <v>71.545</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="3">
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="5" customFormat="1" spans="1:8">
+      <c r="A8" s="10"/>
+      <c r="B8" s="7">
         <v>3</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="5">
         <v>97.8856793452236</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
         <v>81.32</v>
       </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="A9" s="7"/>
-      <c r="B9" s="3">
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="5" customFormat="1" spans="1:8">
+      <c r="A9" s="11"/>
+      <c r="B9" s="7">
         <v>4</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="5">
         <v>97.257829248348</v>
       </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
         <v>87.731</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="6">
         <v>1</v>
       </c>
       <c r="C10">
@@ -1356,8 +1366,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="4"/>
-      <c r="B11" s="2">
+      <c r="A11" s="8"/>
+      <c r="B11" s="6">
         <v>2</v>
       </c>
       <c r="C11">
@@ -1380,8 +1390,8 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="4"/>
-      <c r="B12" s="2">
+      <c r="A12" s="8"/>
+      <c r="B12" s="6">
         <v>3</v>
       </c>
       <c r="C12">
@@ -1404,8 +1414,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="5"/>
-      <c r="B13" s="2">
+      <c r="A13" s="9"/>
+      <c r="B13" s="6">
         <v>4</v>
       </c>
       <c r="C13">
@@ -1445,36 +1455,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C2">
@@ -1497,8 +1507,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C3">
@@ -1521,8 +1531,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C4">
@@ -1545,8 +1555,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C5">
@@ -1569,8 +1579,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C6">
@@ -1592,133 +1602,133 @@
         <v>98.859</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="A7" s="3" t="s">
+    <row r="7" s="5" customFormat="1" spans="1:8">
+      <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="5">
         <v>97.2202576966429</v>
       </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
         <v>90.808</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="5" customFormat="1" spans="1:8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="5">
         <v>97.2230203107388</v>
       </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
         <v>91.56</v>
       </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="5" customFormat="1" spans="1:8">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="5">
         <v>97.3489955135147</v>
       </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
         <v>91.857</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="5" customFormat="1" spans="1:8">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="5">
         <v>97.4611576458108</v>
       </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
         <v>54.616</v>
       </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3" t="s">
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="5" customFormat="1" spans="1:8">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="5">
         <v>97.257829248348</v>
       </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
         <v>87.731</v>
       </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C12">
@@ -1741,8 +1751,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C13">
@@ -1765,8 +1775,8 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C14">
@@ -1789,8 +1799,8 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C15">
@@ -1813,8 +1823,8 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C16">
@@ -1845,4 +1855,576 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2">
+        <v>99.9690592288971</v>
+      </c>
+      <c r="D2" s="2">
+        <v>99.9621152877808</v>
+      </c>
+      <c r="E2" s="2">
+        <v>99.265</v>
+      </c>
+      <c r="F2" s="2">
+        <v>99.423</v>
+      </c>
+      <c r="G2" s="2">
+        <v>99.261</v>
+      </c>
+      <c r="H2" s="2">
+        <v>99.593</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2">
+        <v>99.9657422304153</v>
+      </c>
+      <c r="D3" s="2">
+        <v>99.9372363090515</v>
+      </c>
+      <c r="E3" s="2">
+        <v>99.891</v>
+      </c>
+      <c r="F3" s="2">
+        <v>99.892</v>
+      </c>
+      <c r="G3" s="2">
+        <v>99.863</v>
+      </c>
+      <c r="H3" s="2">
+        <v>99.921</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2">
+        <v>99.9701678752899</v>
+      </c>
+      <c r="D4" s="2">
+        <v>99.9629259109497</v>
+      </c>
+      <c r="E4" s="2">
+        <v>99.842</v>
+      </c>
+      <c r="F4" s="2">
+        <v>99.835</v>
+      </c>
+      <c r="G4" s="2">
+        <v>99.826</v>
+      </c>
+      <c r="H4" s="2">
+        <v>99.844</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>99.9580085277557</v>
+      </c>
+      <c r="D5" s="2">
+        <v>99.946403503418</v>
+      </c>
+      <c r="E5" s="2">
+        <v>96.627</v>
+      </c>
+      <c r="F5" s="2">
+        <v>93.584</v>
+      </c>
+      <c r="G5" s="2">
+        <v>91.547</v>
+      </c>
+      <c r="H5" s="2">
+        <v>95.992</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>99.9651879072189</v>
+      </c>
+      <c r="D6" s="2">
+        <v>99.959397315979</v>
+      </c>
+      <c r="E6" s="2">
+        <v>98.626</v>
+      </c>
+      <c r="F6" s="2">
+        <v>95.785</v>
+      </c>
+      <c r="G6" s="2">
+        <v>98.918</v>
+      </c>
+      <c r="H6" s="2">
+        <v>93.236</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
+        <v>96.5970119565938</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>88.587</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="3"/>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2">
+        <v>96.5644131102615</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>91.803</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2">
+        <v>96.930735739386</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>90.861</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="3"/>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2">
+        <v>96.9771476561982</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>61.718</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2">
+        <v>96.8163635158132</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>86.034</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2">
+        <v>99.9397784471512</v>
+      </c>
+      <c r="D2" s="2">
+        <v>99.9178349971771</v>
+      </c>
+      <c r="E2" s="2">
+        <v>99.407</v>
+      </c>
+      <c r="F2" s="2">
+        <v>99.37</v>
+      </c>
+      <c r="G2" s="2">
+        <v>99.12</v>
+      </c>
+      <c r="H2" s="2">
+        <v>99.625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2">
+        <v>99.9347984790802</v>
+      </c>
+      <c r="D3" s="2">
+        <v>99.8916149139404</v>
+      </c>
+      <c r="E3" s="2">
+        <v>99.813</v>
+      </c>
+      <c r="F3" s="2">
+        <v>99.832</v>
+      </c>
+      <c r="G3" s="2">
+        <v>99.797</v>
+      </c>
+      <c r="H3" s="2">
+        <v>99.866</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2">
+        <v>99.9215394258499</v>
+      </c>
+      <c r="D4" s="2">
+        <v>99.9198615550995</v>
+      </c>
+      <c r="E4" s="2">
+        <v>99.701</v>
+      </c>
+      <c r="F4" s="2">
+        <v>99.723</v>
+      </c>
+      <c r="G4" s="2">
+        <v>99.725</v>
+      </c>
+      <c r="H4" s="2">
+        <v>99.722</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>99.9397784471512</v>
+      </c>
+      <c r="D5" s="2">
+        <v>99.9101996421814</v>
+      </c>
+      <c r="E5" s="2">
+        <v>97.461</v>
+      </c>
+      <c r="F5" s="2">
+        <v>90.329</v>
+      </c>
+      <c r="G5" s="2">
+        <v>86.652</v>
+      </c>
+      <c r="H5" s="2">
+        <v>95.508</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>99.9309360980988</v>
+      </c>
+      <c r="D6" s="2">
+        <v>99.8811662197113</v>
+      </c>
+      <c r="E6" s="2">
+        <v>98.413</v>
+      </c>
+      <c r="F6" s="2">
+        <v>96.697</v>
+      </c>
+      <c r="G6" s="2">
+        <v>98.703</v>
+      </c>
+      <c r="H6" s="2">
+        <v>94.951</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
+        <v>95.4151656463412</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>88.397</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2">
+        <v>95.2610117797865</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>91.753</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2">
+        <v>95.4190333060755</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>90.185</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2">
+        <v>96.2710234932703</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>53.607</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2">
+        <v>95.7997215284991</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>85.056</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/results/results_baseline.xlsx
+++ b/results/results_baseline.xlsx
@@ -4,13 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15540" activeTab="3"/>
+    <workbookView windowWidth="30720" windowHeight="15540" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="conv2d_O" sheetId="4" r:id="rId1"/>
     <sheet name="conv2d_T" sheetId="5" r:id="rId2"/>
     <sheet name="conv2d_T_half" sheetId="6" r:id="rId3"/>
     <sheet name="conv2d_T_quarter" sheetId="7" r:id="rId4"/>
+    <sheet name="conv2d_T_RAPL1" sheetId="8" r:id="rId5"/>
+    <sheet name="conv2d_T_RAPL2" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="17">
   <si>
     <t>HyperParameters</t>
   </si>
@@ -747,7 +749,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -757,17 +759,20 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1118,36 +1123,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="10">
         <v>1</v>
       </c>
       <c r="C2">
@@ -1170,8 +1175,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="8"/>
-      <c r="B3" s="6">
+      <c r="A3" s="11"/>
+      <c r="B3" s="10">
         <v>2</v>
       </c>
       <c r="C3">
@@ -1194,8 +1199,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="8"/>
-      <c r="B4" s="6">
+      <c r="A4" s="11"/>
+      <c r="B4" s="10">
         <v>3</v>
       </c>
       <c r="C4">
@@ -1218,8 +1223,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="9"/>
-      <c r="B5" s="6">
+      <c r="A5" s="12"/>
+      <c r="B5" s="10">
         <v>4</v>
       </c>
       <c r="C5">
@@ -1241,109 +1246,109 @@
         <v>98.859</v>
       </c>
     </row>
-    <row r="6" s="5" customFormat="1" spans="1:8">
-      <c r="A6" s="7" t="s">
+    <row r="6" s="9" customFormat="1" spans="1:8">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>1</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="9">
         <v>97.7147656198201</v>
       </c>
-      <c r="D6" s="5">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9">
         <v>62.172</v>
       </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="5" customFormat="1" spans="1:8">
-      <c r="A7" s="10"/>
-      <c r="B7" s="7">
+      <c r="F6" s="9">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="9" customFormat="1" spans="1:8">
+      <c r="A7" s="7"/>
+      <c r="B7" s="5">
         <v>2</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="9">
         <v>97.8451610051495</v>
       </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
         <v>71.545</v>
       </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="5" customFormat="1" spans="1:8">
-      <c r="A8" s="10"/>
-      <c r="B8" s="7">
+      <c r="F7" s="9">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="9" customFormat="1" spans="1:8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="5">
         <v>3</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="9">
         <v>97.8856793452236</v>
       </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
         <v>81.32</v>
       </c>
-      <c r="F8" s="5">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="5" customFormat="1" spans="1:8">
-      <c r="A9" s="11"/>
-      <c r="B9" s="7">
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="9" customFormat="1" spans="1:8">
+      <c r="A9" s="8"/>
+      <c r="B9" s="5">
         <v>4</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="9">
         <v>97.257829248348</v>
       </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
         <v>87.731</v>
       </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
+      <c r="F9" s="9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="10">
         <v>1</v>
       </c>
       <c r="C10">
@@ -1366,8 +1371,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8"/>
-      <c r="B11" s="6">
+      <c r="A11" s="11"/>
+      <c r="B11" s="10">
         <v>2</v>
       </c>
       <c r="C11">
@@ -1390,8 +1395,8 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="8"/>
-      <c r="B12" s="6">
+      <c r="A12" s="11"/>
+      <c r="B12" s="10">
         <v>3</v>
       </c>
       <c r="C12">
@@ -1414,8 +1419,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="9"/>
-      <c r="B13" s="6">
+      <c r="A13" s="12"/>
+      <c r="B13" s="10">
         <v>4</v>
       </c>
       <c r="C13">
@@ -1455,36 +1460,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C2">
@@ -1507,8 +1512,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C3">
@@ -1531,8 +1536,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C4">
@@ -1555,8 +1560,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C5">
@@ -1579,8 +1584,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C6">
@@ -1602,133 +1607,133 @@
         <v>98.859</v>
       </c>
     </row>
-    <row r="7" s="5" customFormat="1" spans="1:8">
-      <c r="A7" s="7" t="s">
+    <row r="7" s="9" customFormat="1" spans="1:8">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="9">
         <v>97.2202576966429</v>
       </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
         <v>90.808</v>
       </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="5" customFormat="1" spans="1:8">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7" t="s">
+      <c r="F7" s="9">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="9" customFormat="1" spans="1:8">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="9">
         <v>97.2230203107388</v>
       </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
         <v>91.56</v>
       </c>
-      <c r="F8" s="5">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="5" customFormat="1" spans="1:8">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7" t="s">
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="9" customFormat="1" spans="1:8">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="9">
         <v>97.3489955135147</v>
       </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
         <v>91.857</v>
       </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="5" customFormat="1" spans="1:8">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7" t="s">
+      <c r="F9" s="9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="9" customFormat="1" spans="1:8">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="9">
         <v>97.4611576458108</v>
       </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
         <v>54.616</v>
       </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="5" customFormat="1" spans="1:8">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7" t="s">
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="9" customFormat="1" spans="1:8">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="9">
         <v>97.257829248348</v>
       </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9">
         <v>87.731</v>
       </c>
-      <c r="F11" s="5">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C12">
@@ -1751,8 +1756,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C13">
@@ -1775,8 +1780,8 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C14">
@@ -1799,8 +1804,8 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C15">
@@ -1823,8 +1828,8 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C16">
@@ -1860,6 +1865,824 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="6">
+        <v>99.9690592288971</v>
+      </c>
+      <c r="D2" s="6">
+        <v>99.9621152877808</v>
+      </c>
+      <c r="E2" s="6">
+        <v>99.265</v>
+      </c>
+      <c r="F2" s="6">
+        <v>99.423</v>
+      </c>
+      <c r="G2" s="6">
+        <v>99.261</v>
+      </c>
+      <c r="H2" s="6">
+        <v>99.593</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="7"/>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="6">
+        <v>99.9657422304153</v>
+      </c>
+      <c r="D3" s="6">
+        <v>99.9372363090515</v>
+      </c>
+      <c r="E3" s="6">
+        <v>99.891</v>
+      </c>
+      <c r="F3" s="6">
+        <v>99.892</v>
+      </c>
+      <c r="G3" s="6">
+        <v>99.863</v>
+      </c>
+      <c r="H3" s="6">
+        <v>99.921</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="7"/>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="6">
+        <v>99.9701678752899</v>
+      </c>
+      <c r="D4" s="6">
+        <v>99.9629259109497</v>
+      </c>
+      <c r="E4" s="6">
+        <v>99.842</v>
+      </c>
+      <c r="F4" s="6">
+        <v>99.835</v>
+      </c>
+      <c r="G4" s="6">
+        <v>99.826</v>
+      </c>
+      <c r="H4" s="6">
+        <v>99.844</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="7"/>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6">
+        <v>99.9580085277557</v>
+      </c>
+      <c r="D5" s="6">
+        <v>99.946403503418</v>
+      </c>
+      <c r="E5" s="6">
+        <v>96.627</v>
+      </c>
+      <c r="F5" s="6">
+        <v>93.584</v>
+      </c>
+      <c r="G5" s="6">
+        <v>91.547</v>
+      </c>
+      <c r="H5" s="6">
+        <v>95.992</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="8"/>
+      <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6">
+        <v>99.9651879072189</v>
+      </c>
+      <c r="D6" s="6">
+        <v>99.959397315979</v>
+      </c>
+      <c r="E6" s="6">
+        <v>98.626</v>
+      </c>
+      <c r="F6" s="6">
+        <v>95.785</v>
+      </c>
+      <c r="G6" s="6">
+        <v>98.918</v>
+      </c>
+      <c r="H6" s="6">
+        <v>93.236</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6">
+        <v>96.5970119565938</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>88.587</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="6">
+        <v>96.5644131102615</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>91.803</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="7"/>
+      <c r="B9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="6">
+        <v>96.930735739386</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>90.861</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="7"/>
+      <c r="B10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="6">
+        <v>96.9771476561982</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>61.718</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="8"/>
+      <c r="B11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="6">
+        <v>96.8163635158132</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>86.034</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="6">
+        <v>99.871814250946</v>
+      </c>
+      <c r="D12" s="6">
+        <v>99.6801316738129</v>
+      </c>
+      <c r="E12" s="6">
+        <v>97.738</v>
+      </c>
+      <c r="F12" s="6">
+        <v>94.13</v>
+      </c>
+      <c r="G12" s="6">
+        <v>93.138</v>
+      </c>
+      <c r="H12" s="6">
+        <v>95.184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="7"/>
+      <c r="B13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="6">
+        <v>99.8685002326965</v>
+      </c>
+      <c r="D13" s="6">
+        <v>99.6717095375061</v>
+      </c>
+      <c r="E13" s="6">
+        <v>99.18</v>
+      </c>
+      <c r="F13" s="6">
+        <v>97.897</v>
+      </c>
+      <c r="G13" s="6">
+        <v>97.365</v>
+      </c>
+      <c r="H13" s="6">
+        <v>98.444</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="7"/>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="6">
+        <v>99.6690392494202</v>
+      </c>
+      <c r="D14" s="6">
+        <v>99.1678774356842</v>
+      </c>
+      <c r="E14" s="6">
+        <v>97.836</v>
+      </c>
+      <c r="F14" s="6">
+        <v>94.073</v>
+      </c>
+      <c r="G14" s="6">
+        <v>90.862</v>
+      </c>
+      <c r="H14" s="6">
+        <v>98.041</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="7"/>
+      <c r="B15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="6">
+        <v>99.919331073761</v>
+      </c>
+      <c r="D15" s="6">
+        <v>99.7983813285828</v>
+      </c>
+      <c r="E15" s="6">
+        <v>66.587</v>
+      </c>
+      <c r="F15" s="6">
+        <v>56.505</v>
+      </c>
+      <c r="G15" s="6">
+        <v>73.851</v>
+      </c>
+      <c r="H15" s="6">
+        <v>59.735</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="8"/>
+      <c r="B16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="6">
+        <v>99.8740255832672</v>
+      </c>
+      <c r="D16" s="6">
+        <v>99.6850192546844</v>
+      </c>
+      <c r="E16" s="6">
+        <v>98.436</v>
+      </c>
+      <c r="F16" s="6">
+        <v>95.88</v>
+      </c>
+      <c r="G16" s="6">
+        <v>94.177</v>
+      </c>
+      <c r="H16" s="6">
+        <v>97.767</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="6">
+        <v>99.9397784471512</v>
+      </c>
+      <c r="D2" s="6">
+        <v>99.9178349971771</v>
+      </c>
+      <c r="E2" s="6">
+        <v>99.407</v>
+      </c>
+      <c r="F2" s="6">
+        <v>99.37</v>
+      </c>
+      <c r="G2" s="6">
+        <v>99.12</v>
+      </c>
+      <c r="H2" s="6">
+        <v>99.625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="7"/>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="6">
+        <v>99.9347984790802</v>
+      </c>
+      <c r="D3" s="6">
+        <v>99.8916149139404</v>
+      </c>
+      <c r="E3" s="6">
+        <v>99.813</v>
+      </c>
+      <c r="F3" s="6">
+        <v>99.832</v>
+      </c>
+      <c r="G3" s="6">
+        <v>99.797</v>
+      </c>
+      <c r="H3" s="6">
+        <v>99.866</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="7"/>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="6">
+        <v>99.9215394258499</v>
+      </c>
+      <c r="D4" s="6">
+        <v>99.9198615550995</v>
+      </c>
+      <c r="E4" s="6">
+        <v>99.701</v>
+      </c>
+      <c r="F4" s="6">
+        <v>99.723</v>
+      </c>
+      <c r="G4" s="6">
+        <v>99.725</v>
+      </c>
+      <c r="H4" s="6">
+        <v>99.722</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="7"/>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6">
+        <v>99.9397784471512</v>
+      </c>
+      <c r="D5" s="6">
+        <v>99.9101996421814</v>
+      </c>
+      <c r="E5" s="6">
+        <v>97.461</v>
+      </c>
+      <c r="F5" s="6">
+        <v>90.329</v>
+      </c>
+      <c r="G5" s="6">
+        <v>86.652</v>
+      </c>
+      <c r="H5" s="6">
+        <v>95.508</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="8"/>
+      <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6">
+        <v>99.9309360980988</v>
+      </c>
+      <c r="D6" s="6">
+        <v>99.8811662197113</v>
+      </c>
+      <c r="E6" s="6">
+        <v>98.413</v>
+      </c>
+      <c r="F6" s="6">
+        <v>96.697</v>
+      </c>
+      <c r="G6" s="6">
+        <v>98.703</v>
+      </c>
+      <c r="H6" s="6">
+        <v>94.951</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6">
+        <v>95.4151656463412</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>88.397</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="6">
+        <v>95.2610117797865</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>91.753</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="7"/>
+      <c r="B9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="6">
+        <v>95.4190333060755</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>90.185</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="7"/>
+      <c r="B10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="6">
+        <v>96.2710234932703</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>53.607</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="8"/>
+      <c r="B11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="6">
+        <v>95.7997215284991</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>85.056</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="6">
+        <v>99.7668325901031</v>
+      </c>
+      <c r="D12" s="6">
+        <v>99.4172215461731</v>
+      </c>
+      <c r="E12" s="6">
+        <v>97.929</v>
+      </c>
+      <c r="F12" s="6">
+        <v>94.561</v>
+      </c>
+      <c r="G12" s="6">
+        <v>93.052</v>
+      </c>
+      <c r="H12" s="6">
+        <v>96.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="6">
+        <v>99.7651755809784</v>
+      </c>
+      <c r="D13" s="6">
+        <v>99.412202835083</v>
+      </c>
+      <c r="E13" s="6">
+        <v>99.121</v>
+      </c>
+      <c r="F13" s="6">
+        <v>97.728</v>
+      </c>
+      <c r="G13" s="6">
+        <v>96.841</v>
+      </c>
+      <c r="H13" s="6">
+        <v>98.661</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="6">
+        <v>99.8265087604523</v>
+      </c>
+      <c r="D14" s="6">
+        <v>99.5658397674561</v>
+      </c>
+      <c r="E14" s="6">
+        <v>98.045</v>
+      </c>
+      <c r="F14" s="6">
+        <v>94.753</v>
+      </c>
+      <c r="G14" s="6">
+        <v>92.331</v>
+      </c>
+      <c r="H14" s="6">
+        <v>97.577</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="6">
+        <v>99.871814250946</v>
+      </c>
+      <c r="D15" s="6">
+        <v>99.6792078018188</v>
+      </c>
+      <c r="E15" s="6">
+        <v>67.504</v>
+      </c>
+      <c r="F15" s="6">
+        <v>57.166</v>
+      </c>
+      <c r="G15" s="6">
+        <v>74.239</v>
+      </c>
+      <c r="H15" s="6">
+        <v>59.972</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="6">
+        <v>99.6441781520844</v>
+      </c>
+      <c r="D16" s="6">
+        <v>99.1130232810974</v>
+      </c>
+      <c r="E16" s="6">
+        <v>98.389</v>
+      </c>
+      <c r="F16" s="6">
+        <v>95.846</v>
+      </c>
+      <c r="G16" s="6">
+        <v>95.102</v>
+      </c>
+      <c r="H16" s="6">
+        <v>96.624</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
@@ -1891,28 +2714,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>99.9690592288971</v>
+        <v>99.407696723938</v>
       </c>
       <c r="D2" s="2">
-        <v>99.9621152877808</v>
+        <v>98.5144853591919</v>
       </c>
       <c r="E2" s="2">
-        <v>99.265</v>
+        <v>99.191</v>
       </c>
       <c r="F2" s="2">
-        <v>99.423</v>
+        <v>97.906</v>
       </c>
       <c r="G2" s="2">
-        <v>99.261</v>
+        <v>96.966</v>
       </c>
       <c r="H2" s="2">
-        <v>99.593</v>
+        <v>98.897</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1921,22 +2744,22 @@
         <v>13</v>
       </c>
       <c r="C3" s="2">
-        <v>99.9657422304153</v>
+        <v>99.4292438030243</v>
       </c>
       <c r="D3" s="2">
-        <v>99.9372363090515</v>
+        <v>98.5735237598419</v>
       </c>
       <c r="E3" s="2">
-        <v>99.891</v>
+        <v>99.116</v>
       </c>
       <c r="F3" s="2">
-        <v>99.892</v>
+        <v>97.724</v>
       </c>
       <c r="G3" s="2">
-        <v>99.863</v>
+        <v>97.024</v>
       </c>
       <c r="H3" s="2">
-        <v>99.921</v>
+        <v>98.453</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1945,22 +2768,22 @@
         <v>14</v>
       </c>
       <c r="C4" s="2">
-        <v>99.9701678752899</v>
+        <v>99.5342254638672</v>
       </c>
       <c r="D4" s="2">
-        <v>99.9629259109497</v>
+        <v>98.8294243812561</v>
       </c>
       <c r="E4" s="2">
-        <v>99.842</v>
+        <v>97.703</v>
       </c>
       <c r="F4" s="2">
-        <v>99.835</v>
+        <v>93.87</v>
       </c>
       <c r="G4" s="2">
-        <v>99.826</v>
+        <v>91.713</v>
       </c>
       <c r="H4" s="2">
-        <v>99.844</v>
+        <v>96.348</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1969,22 +2792,22 @@
         <v>15</v>
       </c>
       <c r="C5" s="2">
-        <v>99.9580085277557</v>
+        <v>99.6419668197632</v>
       </c>
       <c r="D5" s="2">
-        <v>99.946403503418</v>
+        <v>99.1020023822784</v>
       </c>
       <c r="E5" s="2">
-        <v>96.627</v>
+        <v>64.223</v>
       </c>
       <c r="F5" s="2">
-        <v>93.584</v>
+        <v>53.892</v>
       </c>
       <c r="G5" s="2">
-        <v>91.547</v>
+        <v>69.457</v>
       </c>
       <c r="H5" s="2">
-        <v>95.992</v>
+        <v>57.895</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1993,22 +2816,22 @@
         <v>16</v>
       </c>
       <c r="C6" s="2">
-        <v>99.9651879072189</v>
+        <v>99.4762063026428</v>
       </c>
       <c r="D6" s="2">
-        <v>99.959397315979</v>
+        <v>98.6877202987671</v>
       </c>
       <c r="E6" s="2">
-        <v>98.626</v>
+        <v>98.712</v>
       </c>
       <c r="F6" s="2">
-        <v>95.785</v>
+        <v>96.745</v>
       </c>
       <c r="G6" s="2">
-        <v>98.918</v>
+        <v>96.904</v>
       </c>
       <c r="H6" s="2">
-        <v>93.236</v>
+        <v>96.587</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2019,13 +2842,13 @@
         <v>12</v>
       </c>
       <c r="C7" s="2">
-        <v>96.5970119565938</v>
+        <v>89.04623510951</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>88.587</v>
+        <v>89.468</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
@@ -2043,13 +2866,13 @@
         <v>13</v>
       </c>
       <c r="C8" s="2">
-        <v>96.5644131102615</v>
+        <v>91.5817623267841</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>91.803</v>
+        <v>90.097</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -2067,13 +2890,13 @@
         <v>14</v>
       </c>
       <c r="C9" s="2">
-        <v>96.930735739386</v>
+        <v>92.8746657236944</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="2">
-        <v>90.861</v>
+        <v>86.838</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -2091,13 +2914,13 @@
         <v>15</v>
       </c>
       <c r="C10" s="2">
-        <v>96.9771476561982</v>
+        <v>93.8161646075983</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>61.718</v>
+        <v>50.491</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -2115,13 +2938,13 @@
         <v>16</v>
       </c>
       <c r="C11" s="2">
-        <v>96.8163635158132</v>
+        <v>91.9618980263885</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>86.034</v>
+        <v>86.333</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
@@ -2143,7 +2966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H11"/>
@@ -2177,150 +3000,150 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>99.9397784471512</v>
+        <v>91.8569186907419</v>
       </c>
       <c r="D2" s="2">
-        <v>99.9178349971771</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2">
-        <v>99.407</v>
+        <v>81.078</v>
       </c>
       <c r="F2" s="2">
-        <v>99.37</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
-        <v>99.12</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>99.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1"/>
+      <c r="A3" s="3"/>
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="2">
-        <v>99.9347984790802</v>
+        <v>94.1548610957633</v>
       </c>
       <c r="D3" s="2">
-        <v>99.8916149139404</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2">
-        <v>99.813</v>
+        <v>84.184</v>
       </c>
       <c r="F3" s="2">
-        <v>99.832</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2">
-        <v>99.797</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>99.866</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1"/>
+      <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="2">
-        <v>99.9215394258499</v>
+        <v>94.1681216434239</v>
       </c>
       <c r="D4" s="2">
-        <v>99.9198615550995</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>99.701</v>
+        <v>84.14</v>
       </c>
       <c r="F4" s="2">
-        <v>99.723</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>99.725</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>99.722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1"/>
+      <c r="A5" s="3"/>
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="2">
-        <v>99.9397784471512</v>
+        <v>95.3129489247906</v>
       </c>
       <c r="D5" s="2">
-        <v>99.9101996421814</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>97.461</v>
+        <v>45.53</v>
       </c>
       <c r="F5" s="2">
-        <v>90.329</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>86.652</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>95.508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2">
-        <v>99.9309360980988</v>
+        <v>94.5885915088293</v>
       </c>
       <c r="D6" s="2">
-        <v>99.8811662197113</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>98.413</v>
+        <v>78.881</v>
       </c>
       <c r="F6" s="2">
-        <v>96.697</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>98.703</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>94.951</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2">
-        <v>95.4151656463412</v>
+        <v>99.4524478912354</v>
       </c>
       <c r="D7" s="2">
-        <v>0</v>
+        <v>98.6212432384491</v>
       </c>
       <c r="E7" s="2">
-        <v>88.397</v>
+        <v>97.794</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>94.252</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>93.094</v>
       </c>
       <c r="H7" s="2">
-        <v>0</v>
+        <v>95.497</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2329,22 +3152,22 @@
         <v>13</v>
       </c>
       <c r="C8" s="2">
-        <v>95.2610117797865</v>
+        <v>99.6966660022736</v>
       </c>
       <c r="D8" s="2">
-        <v>0</v>
+        <v>99.2384552955627</v>
       </c>
       <c r="E8" s="2">
-        <v>91.753</v>
+        <v>98.58</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>96.34</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>95.619</v>
       </c>
       <c r="H8" s="2">
-        <v>0</v>
+        <v>97.092</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2353,22 +3176,22 @@
         <v>14</v>
       </c>
       <c r="C9" s="2">
-        <v>95.4190333060755</v>
+        <v>99.7314751148224</v>
       </c>
       <c r="D9" s="2">
-        <v>0</v>
+        <v>99.327278137207</v>
       </c>
       <c r="E9" s="2">
-        <v>90.185</v>
+        <v>97.632</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>93.694</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>91.643</v>
       </c>
       <c r="H9" s="2">
-        <v>0</v>
+        <v>96.036</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2377,22 +3200,22 @@
         <v>15</v>
       </c>
       <c r="C10" s="2">
-        <v>96.2710234932703</v>
+        <v>99.865186214447</v>
       </c>
       <c r="D10" s="2">
-        <v>0</v>
+        <v>99.663245677948</v>
       </c>
       <c r="E10" s="2">
-        <v>53.607</v>
+        <v>67.991</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>57.084</v>
       </c>
       <c r="G10" s="2">
-        <v>0</v>
+        <v>72.936</v>
       </c>
       <c r="H10" s="2">
-        <v>0</v>
+        <v>59.547</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2401,22 +3224,22 @@
         <v>16</v>
       </c>
       <c r="C11" s="2">
-        <v>95.7997215284991</v>
+        <v>99.7519195079803</v>
       </c>
       <c r="D11" s="2">
-        <v>0</v>
+        <v>99.3785321712494</v>
       </c>
       <c r="E11" s="2">
-        <v>85.056</v>
+        <v>96.668</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>91.42</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>90.805</v>
       </c>
       <c r="H11" s="2">
-        <v>0</v>
+        <v>92.06</v>
       </c>
     </row>
   </sheetData>
